--- a/healthcare_assessment_forms/011_footwear_wear_analysis_intake_form--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/011_footwear_wear_analysis_intake_form--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'front_left_foot',_'label':_'front_left_foot'}</t>
+          <t>front_left_foot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'front_left_foot', 'label': 'Front Left Foot'}</t>
+          <t>Front Left Foot</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'back_left_foot',_'label':_'back_left_foot'}</t>
+          <t>back_left_foot</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'back_left_foot', 'label': 'Back Left Foot'}</t>
+          <t>Back Left Foot</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'front_right_foot',_'label':_'front_right_foot'}</t>
+          <t>front_right_foot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'front_right_foot', 'label': 'Front Right Foot'}</t>
+          <t>Front Right Foot</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'back_right_foot',_'label':_'back_right_foot'}</t>
+          <t>back_right_foot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'back_right_foot', 'label': 'Back Right Foot'}</t>
+          <t>Back Right Foot</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily_wear',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'daily_wear', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasional_use',_'label':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'occasional_use', 'label': 'Occasional'}</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'custom',_'label':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'custom', 'label': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'stock',_'label':_'stock'}</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'stock', 'label': 'Stock'}</t>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
